--- a/DateBase/orders/Dang Nguyen48_2026-7-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-4.xlsx
@@ -521,6 +521,9 @@
       <c r="C11" t="str">
         <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
       </c>
+      <c r="F11" t="str">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -579,7 +582,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01540030510205120</v>
+        <v>015400305102051230</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -525,9 +525,91 @@
         <v>30</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>548_白星花_tweedia white_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3</v>
+      </c>
+      <c r="C14" t="str">
+        <v>637_干花小盼草红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>4</v>
+      </c>
+      <c r="C15" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v>846_玛格丽特_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5</v>
+      </c>
+      <c r="C17" t="str">
+        <v>540_糖棉_gomphocarpus fruticosus_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>6</v>
+      </c>
+      <c r="C18" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v>143_黑巴克_Black Baccara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -582,7 +664,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>015400305102051230</v>
+        <v>0154003051020512301020108155105</v>
       </c>
     </row>
   </sheetData>
